--- a/dist/Datas/documents/source_publipostage_sans_TMHF.xlsx
+++ b/dist/Datas/documents/source_publipostage_sans_TMHF.xlsx
@@ -517,62 +517,62 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>16788</v>
+        <v>18929</v>
       </c>
       <c r="B2" t="n">
-        <v>908</v>
+        <v>691</v>
       </c>
       <c r="C2" t="n">
         <v>300</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Killian</t>
+          <t>Sylvain</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>BLENO</t>
+          <t>Hurte</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>kbleno.axxel@gmail.com</t>
+          <t>Sylvain.Hurte@ch.toyota-industries.eu</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>AXXEL MANUTENTION</t>
+          <t>Toyota Material Handling Schweiz AG</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>RRE H et RRE H2</t>
+          <t>VECTOR A</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>RRE H et RRE H2</t>
+          <t>VECTOR A</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>1404-T2-TE-49</t>
+          <t>1404-T2-TE-35</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>683</v>
+        <v>711</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>CARQUEFOU 2025 - RRE H et RRE H2</t>
+          <t>BUSSY 2025 - VECTOR A</t>
         </is>
       </c>
       <c r="M2" t="n">
         <v>6</v>
       </c>
       <c r="N2" t="n">
-        <v>2192</v>
+        <v>1984</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>

--- a/dist/Datas/documents/source_publipostage_sans_TMHF.xlsx
+++ b/dist/Datas/documents/source_publipostage_sans_TMHF.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:T5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -514,78 +514,372 @@
           <t>duration_in_hours</t>
         </is>
       </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>formateur</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>lieu</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>fmc</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>18929</v>
+        <v>19054</v>
       </c>
       <c r="B2" t="n">
-        <v>691</v>
+        <v>1545</v>
       </c>
       <c r="C2" t="n">
         <v>300</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Sylvain</t>
+          <t>SHAKIR</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Hurte</t>
+          <t>BUCKLEY</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sylvain.Hurte@ch.toyota-industries.eu</t>
+          <t>s.buckley@poutou.fr</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Toyota Material Handling Schweiz AG</t>
+          <t>POUTOU MANUTENTION</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>VECTOR A</t>
+          <t>BASES TONERO</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>VECTOR A</t>
+          <t>BASES TONERO</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>1404-T2-TE-35</t>
+          <t>1404-T2-TE-65</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>711</v>
+        <v>797</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>BUSSY 2025 - VECTOR A</t>
+          <t>CARQUEFOU 2026 - BASES TONERO</t>
         </is>
       </c>
       <c r="M2" t="n">
         <v>6</v>
       </c>
       <c r="N2" t="n">
-        <v>1984</v>
+        <v>2334</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>2025-09-09 13:30</t>
+          <t>2026-03-31 13:30</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2025-09-12 12:00</t>
+          <t>2026-04-03 12:00</t>
         </is>
       </c>
       <c r="Q2" t="n">
         <v>24</v>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>Bruno LE BEC</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>CARQUEFOU</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>CARQUEFOU</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>19341</v>
+      </c>
+      <c r="B3" t="n">
+        <v>1545</v>
+      </c>
+      <c r="C3" t="n">
+        <v>300</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Guillaume</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>MORENO</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>g.moreno@poutou.fr</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>POUTOU MANUTENTION</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>BASES TONERO</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>BASES TONERO</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>1404-T2-TE-65</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>797</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>CARQUEFOU 2026 - BASES TONERO</t>
+        </is>
+      </c>
+      <c r="M3" t="n">
+        <v>6</v>
+      </c>
+      <c r="N3" t="n">
+        <v>2334</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>2026-03-31 13:30</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2026-04-03 12:00</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>24</v>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>Bruno LE BEC</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>CARQUEFOU</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>CARQUEFOU</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>19352</v>
+      </c>
+      <c r="B4" t="n">
+        <v>1545</v>
+      </c>
+      <c r="C4" t="n">
+        <v>300</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>William</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>JANNEAU</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>w.janneau@poutou.fr</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>POUTOU MANUTENTION</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>BASES TONERO</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>BASES TONERO</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>1404-T2-TE-65</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>797</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>CARQUEFOU 2026 - BASES TONERO</t>
+        </is>
+      </c>
+      <c r="M4" t="n">
+        <v>6</v>
+      </c>
+      <c r="N4" t="n">
+        <v>2334</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>2026-03-31 13:30</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>2026-04-03 12:00</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>24</v>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>Bruno LE BEC</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>CARQUEFOU</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>CARQUEFOU</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>19702</v>
+      </c>
+      <c r="B5" t="n">
+        <v>1545</v>
+      </c>
+      <c r="C5" t="n">
+        <v>300</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Romain</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Turi</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>r.turi@abmmanutention.fr</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>ALLIANCE BOIS MATERIEL</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>BASES TONERO</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>BASES TONERO</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>1404-T2-TE-65</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>797</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>CARQUEFOU 2026 - BASES TONERO</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
+        <v>6</v>
+      </c>
+      <c r="N5" t="n">
+        <v>2334</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>2026-03-31 13:30</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>2026-04-03 12:00</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>24</v>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>Bruno LE BEC</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>CARQUEFOU</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>CARQUEFOU</t>
+        </is>
       </c>
     </row>
   </sheetData>
